--- a/artfynd/S 214-2023 artfynd.xlsx
+++ b/artfynd/S 214-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY139"/>
+  <dimension ref="A1:AZ139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98347056</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165004</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164986</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266777</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164369</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164985</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165002</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165018</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165032</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266802</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1155679</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165037</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165038</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266753</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266754</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165027</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164988</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2545,6 +2640,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164362</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164384</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165028</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3030,6 +3150,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165029</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3127,6 +3252,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165035</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3233,6 +3363,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89897152</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3334,6 +3469,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89897899</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3435,6 +3575,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93540305</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3546,6 +3691,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121172188</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3655,6 +3805,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124637699</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3752,6 +3907,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164366</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3849,6 +4009,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164367</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3946,6 +4111,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164370</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4043,6 +4213,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164371</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4140,6 +4315,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164373</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4237,6 +4417,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164375</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4334,6 +4519,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164377</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4431,6 +4621,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164379</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4528,6 +4723,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164382</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4625,6 +4825,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164385</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4722,6 +4927,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164386</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4819,6 +5029,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164389</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4938,6 +5153,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906500</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5062,6 +5282,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906483</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5186,6 +5411,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906469</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5305,6 +5535,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906499</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5402,6 +5637,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164397</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5526,6 +5766,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906448</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5623,6 +5868,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165020</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5747,6 +5997,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906457</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5866,6 +6121,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906497</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5985,6 +6245,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906505</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6082,6 +6347,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164396</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6205,6 +6475,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102494021</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6324,6 +6599,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906506</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6443,6 +6723,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906596</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6562,6 +6847,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906490</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6682,6 +6972,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906495</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6797,6 +7092,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119906540</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6906,6 +7206,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89897531</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7017,6 +7322,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2196319</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7114,6 +7424,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164352</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7211,6 +7526,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266820</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7308,6 +7628,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266821</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7424,6 +7749,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2454567</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7521,6 +7851,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164353</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7618,6 +7953,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164354</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7715,6 +8055,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164355</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7812,6 +8157,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164356</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7909,6 +8259,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164357</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8006,6 +8361,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164358</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8103,6 +8463,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164359</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8200,6 +8565,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164360</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8297,6 +8667,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164363</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8394,6 +8769,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164364</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8491,6 +8871,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164365</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8588,6 +8973,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164368</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8685,6 +9075,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164372</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8782,6 +9177,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164374</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8879,6 +9279,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164376</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8976,6 +9381,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164378</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9073,6 +9483,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164380</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9170,6 +9585,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164383</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9267,6 +9687,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164387</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9364,6 +9789,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164390</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9461,6 +9891,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164399</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9558,6 +9993,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164400</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9655,6 +10095,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164401</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9752,6 +10197,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164402</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9849,6 +10299,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164987</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9959,6 +10414,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83429727</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10074,6 +10534,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110518495</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10189,6 +10654,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110518497</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10304,6 +10774,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110518499</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10414,6 +10889,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110585907</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10529,6 +11009,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110469654</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10644,6 +11129,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110507418</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10741,6 +11231,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121198727</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10838,6 +11333,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266705</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10940,6 +11440,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3907293</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11037,6 +11542,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165017</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11134,6 +11644,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165039</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11236,6 +11751,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5028616</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11333,6 +11853,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164347</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11430,6 +11955,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164349</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11527,6 +12057,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164351</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11624,6 +12159,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164393</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11721,6 +12261,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164394</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11818,6 +12363,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164395</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11915,6 +12465,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164398</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12012,6 +12567,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164992</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12109,6 +12669,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164995</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12206,6 +12771,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164998</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12303,6 +12873,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164999</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12400,6 +12975,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165000</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12497,6 +13077,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165003</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12594,6 +13179,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165008</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12691,6 +13281,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165009</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12788,6 +13383,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165016</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12885,6 +13485,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165023</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12982,6 +13587,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165025</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13079,6 +13689,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165040</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13185,6 +13800,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108606242</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13282,6 +13902,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115698139</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13379,6 +14004,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266727</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13476,6 +14106,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266728</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13578,6 +14213,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5260754</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13675,6 +14315,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165014</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13772,6 +14417,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165015</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13869,6 +14519,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164361</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13966,6 +14621,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73164994</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14063,6 +14723,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73165010</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14160,6 +14825,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266796</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14257,6 +14927,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266797</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14354,6 +15029,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266810</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14451,6 +15131,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266778</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14561,6 +15246,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83432775</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14676,8 +15366,153 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110467510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>